--- a/docs/StructureDefinition-lbnp-pressure-level.xlsx
+++ b/docs/StructureDefinition-lbnp-pressure-level.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-lbnp-pressure-level.xlsx
+++ b/docs/StructureDefinition-lbnp-pressure-level.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="156">
   <si>
     <t>Property</t>
   </si>
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/StructureDefinition/lbnp-pressure-level</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/lbnp-pressure-level</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -88,6 +88,9 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -735,70 +738,72 @@
       <c r="A14" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -851,123 +856,123 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -975,10 +980,10 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -990,7 +995,7 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L2" t="s" s="2">
         <v>9</v>
@@ -1047,19 +1052,19 @@
         <v>20</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>20</v>
@@ -1067,10 +1072,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1078,10 +1083,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -1093,13 +1098,13 @@
         <v>20</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1150,13 +1155,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -1165,15 +1170,15 @@
         <v>20</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1181,10 +1186,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -1196,13 +1201,13 @@
         <v>20</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1241,31 +1246,31 @@
         <v>20</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AD4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -1273,10 +1278,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1284,10 +1289,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
@@ -1299,16 +1304,16 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1358,13 +1363,13 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
@@ -1373,15 +1378,15 @@
         <v>20</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1389,10 +1394,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -1404,13 +1409,13 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1461,30 +1466,30 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AG6" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH6" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK6" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="AG6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH6" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ6" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK6" t="s" s="2">
-        <v>101</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1492,10 +1497,10 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -1507,13 +1512,13 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1564,13 +1569,13 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
@@ -1579,26 +1584,26 @@
         <v>20</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -1610,16 +1615,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1657,42 +1662,42 @@
         <v>20</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AD8" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1700,10 +1705,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -1712,22 +1717,22 @@
         <v>20</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O9" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P9" t="s" s="2">
         <v>20</v>
@@ -1776,30 +1781,30 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1807,38 +1812,38 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q10" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="R10" t="s" s="2">
         <v>20</v>
@@ -1859,13 +1864,13 @@
         <v>20</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AA10" t="s" s="2">
         <v>20</v>
@@ -1883,30 +1888,30 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1914,10 +1919,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
@@ -1926,20 +1931,20 @@
         <v>20</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -1988,30 +1993,30 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2019,10 +2024,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
@@ -2031,20 +2036,20 @@
         <v>20</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>20</v>
@@ -2054,7 +2059,7 @@
         <v>20</v>
       </c>
       <c r="S12" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="T12" t="s" s="2">
         <v>20</v>
@@ -2093,30 +2098,30 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2124,10 +2129,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
@@ -2136,22 +2141,22 @@
         <v>20</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>20</v>
@@ -2161,7 +2166,7 @@
         <v>20</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="T13" t="s" s="2">
         <v>20</v>
@@ -2200,22 +2205,22 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
